--- a/tabular/sublineage/herv_sublineage_data.xlsx
+++ b/tabular/sublineage/herv_sublineage_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/sublineage/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8AA2845-B672-BA4C-A670-2A0BE99A5571}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B828DC8D-DAFA-1845-860C-B35390FBC2C1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1240" yWindow="500" windowWidth="23060" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10520" yWindow="1380" windowWidth="23060" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sublineage" sheetId="2" r:id="rId1"/>
@@ -537,9 +537,6 @@
     <t>ERV-1.Gamma.T</t>
   </si>
   <si>
-    <t>ERV-3.Lamba.L</t>
-  </si>
-  <si>
     <t>ERV-1.Zeta</t>
   </si>
   <si>
@@ -630,9 +627,6 @@
     <t>ERV-1.Zeta.W9P.P</t>
   </si>
   <si>
-    <t>ERV-1.Zeta.W9P.P.G25</t>
-  </si>
-  <si>
     <t>phylogeny_group</t>
   </si>
   <si>
@@ -736,6 +730,12 @@
   </si>
   <si>
     <t>ERV-1.Eta.E.HQ</t>
+  </si>
+  <si>
+    <t>ERV-1.Iota.I</t>
+  </si>
+  <si>
+    <t>ERVR-1.Zeta.W9P.P.G25</t>
   </si>
 </sst>
 </file>
@@ -1698,7 +1698,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>68</v>
@@ -1710,13 +1710,13 @@
         <v>82</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>156</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>157</v>
@@ -1767,7 +1767,7 @@
         <v>104</v>
       </c>
       <c r="Y1" s="4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.2">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>161</v>
@@ -1812,7 +1812,7 @@
         <v>5</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="P2" s="1"/>
       <c r="Q2" s="2" t="s">
@@ -1825,7 +1825,7 @@
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
       <c r="V2" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="W2" s="2" t="s">
         <v>11</v>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>161</v>
@@ -1882,7 +1882,7 @@
         <v>54</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>6</v>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>161</v>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>161</v>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="s">
-        <v>168</v>
+        <v>106</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>161</v>
@@ -2446,20 +2446,20 @@
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>161</v>
@@ -2468,7 +2468,7 @@
         <v>105</v>
       </c>
       <c r="I12" s="16" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>12</v>
@@ -2483,7 +2483,7 @@
         <v>5</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="P12" s="2"/>
       <c r="Q12" s="2" t="s">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>161</v>
@@ -2529,7 +2529,7 @@
         <v>105</v>
       </c>
       <c r="I13" s="16" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>12</v>
@@ -2547,7 +2547,7 @@
         <v>5</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="P13" s="1"/>
       <c r="Q13" s="2" t="s">
@@ -2560,7 +2560,7 @@
       <c r="T13" s="2"/>
       <c r="U13" s="2"/>
       <c r="V13" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="W13" s="2" t="s">
         <v>11</v>
@@ -2596,7 +2596,7 @@
         <v>105</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>160</v>
@@ -2644,7 +2644,7 @@
         <v>83</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>83</v>
@@ -2654,10 +2654,10 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>105</v>
@@ -2713,7 +2713,7 @@
         <v>59</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>59</v>
@@ -2723,10 +2723,10 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>200</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>105</v>
@@ -2753,7 +2753,7 @@
         <v>54</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="Q16" s="2" t="s">
         <v>6</v>
@@ -2784,7 +2784,7 @@
         <v>60</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>60</v>
@@ -2794,10 +2794,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>200</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>105</v>
@@ -2824,7 +2824,7 @@
         <v>54</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="Q17" s="2" t="s">
         <v>6</v>
@@ -2852,23 +2852,23 @@
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>200</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>105</v>
@@ -2895,7 +2895,7 @@
         <v>54</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="Q18" s="2" t="s">
         <v>13</v>
@@ -2936,7 +2936,7 @@
         <v>106</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>105</v>
@@ -2963,7 +2963,7 @@
         <v>19</v>
       </c>
       <c r="P19" s="13" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="Q19" s="2" t="s">
         <v>6</v>
@@ -3005,7 +3005,7 @@
         <v>106</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>105</v>
@@ -3032,7 +3032,7 @@
         <v>19</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="Q20" s="2" t="s">
         <v>6</v>
@@ -3074,7 +3074,7 @@
         <v>106</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>105</v>
@@ -3128,7 +3128,7 @@
         <v>41</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>41</v>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>162</v>
@@ -3195,7 +3195,7 @@
         <v>43</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>43</v>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>162</v>
@@ -3262,7 +3262,7 @@
         <v>44</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>44</v>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>162</v>
@@ -3329,7 +3329,7 @@
         <v>50</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>50</v>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>162</v>
@@ -3396,7 +3396,7 @@
         <v>52</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>52</v>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>162</v>
@@ -3463,7 +3463,7 @@
         <v>58</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>199</v>
+        <v>234</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>58</v>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>162</v>
@@ -3503,7 +3503,7 @@
         <v>54</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="Q27" s="2" t="s">
         <v>6</v>
@@ -3532,7 +3532,7 @@
         <v>62</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>62</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>162</v>
@@ -3599,7 +3599,7 @@
         <v>64</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>64</v>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>162</v>
@@ -3666,7 +3666,7 @@
         <v>65</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>65</v>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>162</v>
@@ -3733,7 +3733,7 @@
         <v>66</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>66</v>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>162</v>
@@ -3800,7 +3800,7 @@
         <v>67</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>67</v>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>162</v>
@@ -3864,16 +3864,16 @@
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A33" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2" t="s">
@@ -3936,7 +3936,7 @@
         <v>31</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>31</v>
@@ -3946,7 +3946,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2" t="s">
-        <v>168</v>
+        <v>106</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>162</v>
@@ -4003,7 +4003,7 @@
         <v>32</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>32</v>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="2" t="s">
-        <v>168</v>
+        <v>106</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>162</v>
@@ -4070,7 +4070,7 @@
         <v>40</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>40</v>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>162</v>
@@ -4089,7 +4089,7 @@
         <v>105</v>
       </c>
       <c r="I36" s="16" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>12</v>
@@ -4137,7 +4137,7 @@
         <v>42</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>42</v>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>162</v>
@@ -4156,7 +4156,7 @@
         <v>105</v>
       </c>
       <c r="I37" s="16" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>12</v>
@@ -4204,7 +4204,7 @@
         <v>45</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>45</v>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>162</v>
@@ -4223,7 +4223,7 @@
         <v>105</v>
       </c>
       <c r="I38" s="16" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>12</v>
@@ -4271,7 +4271,7 @@
         <v>46</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>46</v>
@@ -4281,7 +4281,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>162</v>
@@ -4290,7 +4290,7 @@
         <v>105</v>
       </c>
       <c r="I39" s="16" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>12</v>
@@ -4338,7 +4338,7 @@
         <v>47</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>47</v>
@@ -4348,7 +4348,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>162</v>
@@ -4357,7 +4357,7 @@
         <v>105</v>
       </c>
       <c r="I40" s="16" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>12</v>
@@ -4405,7 +4405,7 @@
         <v>48</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>48</v>
@@ -4415,7 +4415,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>162</v>
@@ -4424,7 +4424,7 @@
         <v>105</v>
       </c>
       <c r="I41" s="16" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>12</v>
@@ -4442,7 +4442,7 @@
         <v>5</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P41" s="1"/>
       <c r="Q41" s="2" t="s">
@@ -4472,7 +4472,7 @@
         <v>49</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>49</v>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>162</v>
@@ -4491,7 +4491,7 @@
         <v>105</v>
       </c>
       <c r="I42" s="16" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>12</v>
@@ -4509,7 +4509,7 @@
         <v>5</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P42" s="1"/>
       <c r="Q42" s="2" t="s">
@@ -4539,7 +4539,7 @@
         <v>51</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>51</v>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>162</v>
@@ -4558,7 +4558,7 @@
         <v>105</v>
       </c>
       <c r="I43" s="16" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>12</v>
@@ -4576,7 +4576,7 @@
         <v>5</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P43" s="1"/>
       <c r="Q43" s="2" t="s">
@@ -4696,10 +4696,10 @@
         <v>165</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>156</v>
@@ -4764,22 +4764,22 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>181</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>105</v>
@@ -4807,7 +4807,7 @@
         <v>8</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="S2" s="2" t="s">
         <v>6</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>105</v>
@@ -4880,7 +4880,7 @@
         <v>8</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="S3" s="2" t="s">
         <v>6</v>
@@ -4925,7 +4925,7 @@
         <v>167</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>105</v>
@@ -5002,7 +5002,7 @@
         <v>167</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>105</v>
@@ -5079,7 +5079,7 @@
         <v>167</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>105</v>
@@ -5141,22 +5141,22 @@
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>105</v>
@@ -5174,7 +5174,7 @@
         <v>11</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M7" s="9" t="s">
         <v>3</v>
@@ -5231,7 +5231,7 @@
         <v>106</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>105</v>
@@ -5303,7 +5303,7 @@
         <v>61</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>160</v>
@@ -5448,7 +5448,7 @@
         <v>16</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>16</v>
@@ -5457,10 +5457,10 @@
         <v>89</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>105</v>

--- a/tabular/sublineage/herv_sublineage_data.xlsx
+++ b/tabular/sublineage/herv_sublineage_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/sublineage/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B828DC8D-DAFA-1845-860C-B35390FBC2C1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF21E09-0E87-0841-AC9B-43087069E310}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10520" yWindow="1380" windowWidth="23060" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2220" yWindow="860" windowWidth="23060" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sublineage" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="236">
   <si>
     <t>sequenceID</t>
   </si>
@@ -736,6 +736,9 @@
   </si>
   <si>
     <t>ERVR-1.Zeta.W9P.P.G25</t>
+  </si>
+  <si>
+    <t>ERV-3.Lambda</t>
   </si>
 </sst>
 </file>
@@ -2933,7 +2936,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2" t="s">
-        <v>106</v>
+        <v>235</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>198</v>
@@ -3002,7 +3005,7 @@
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="2" t="s">
-        <v>106</v>
+        <v>235</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>198</v>
@@ -3071,7 +3074,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2" t="s">
-        <v>106</v>
+        <v>235</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>198</v>

--- a/tabular/sublineage/herv_sublineage_data.xlsx
+++ b/tabular/sublineage/herv_sublineage_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/sublineage/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF21E09-0E87-0841-AC9B-43087069E310}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AB9AEB2-E091-B643-A247-E2565DC09B1E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2220" yWindow="860" windowWidth="23060" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1357,7 +1357,17 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1678,7 +1688,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB9083D8-DE01-F14E-ACB5-AF33867092C5}">
-  <dimension ref="A1:Y43"/>
+  <dimension ref="A1:Y42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.33203125" customWidth="1"/>
@@ -2923,18 +2933,18 @@
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E19" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E19" s="3"/>
       <c r="F19" s="2" t="s">
         <v>235</v>
       </c>
@@ -2954,7 +2964,7 @@
         <v>3</v>
       </c>
       <c r="L19" s="2">
-        <v>5667</v>
+        <v>5714</v>
       </c>
       <c r="M19" s="6" t="s">
         <v>18</v>
@@ -2965,7 +2975,7 @@
       <c r="O19" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P19" s="13" t="s">
+      <c r="P19" s="1" t="s">
         <v>210</v>
       </c>
       <c r="Q19" s="2" t="s">
@@ -2984,7 +2994,7 @@
         <v>11</v>
       </c>
       <c r="X19">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y19" s="2" t="b">
         <v>1</v>
@@ -2992,18 +3002,18 @@
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E20" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E20" s="2"/>
       <c r="F20" s="2" t="s">
         <v>235</v>
       </c>
@@ -3017,13 +3027,13 @@
         <v>158</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>11</v>
+        <v>160</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>3</v>
       </c>
       <c r="L20" s="2">
-        <v>5714</v>
+        <v>5246</v>
       </c>
       <c r="M20" s="6" t="s">
         <v>18</v>
@@ -3032,11 +3042,9 @@
         <v>5</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="P20" s="1" t="s">
-        <v>210</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="P20" s="1"/>
       <c r="Q20" s="2" t="s">
         <v>6</v>
       </c>
@@ -3061,23 +3069,23 @@
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>116</v>
+        <v>41</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>204</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2" t="s">
-        <v>235</v>
+        <v>169</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>198</v>
+        <v>162</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>105</v>
@@ -3086,22 +3094,22 @@
         <v>158</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>160</v>
+        <v>12</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>3</v>
       </c>
       <c r="L21" s="2">
-        <v>5246</v>
+        <v>8120</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>5</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P21" s="1"/>
       <c r="Q21" s="2" t="s">
@@ -3114,7 +3122,7 @@
       <c r="T21" s="2"/>
       <c r="U21" s="2"/>
       <c r="V21" s="2" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="W21" s="2" t="s">
         <v>11</v>
@@ -3128,16 +3136,16 @@
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2" t="s">
@@ -3159,7 +3167,7 @@
         <v>3</v>
       </c>
       <c r="L22" s="2">
-        <v>8120</v>
+        <v>4798</v>
       </c>
       <c r="M22" s="6" t="s">
         <v>14</v>
@@ -3195,16 +3203,16 @@
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>43</v>
+        <v>138</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2" t="s">
@@ -3226,7 +3234,7 @@
         <v>3</v>
       </c>
       <c r="L23" s="2">
-        <v>4798</v>
+        <v>6639</v>
       </c>
       <c r="M23" s="6" t="s">
         <v>14</v>
@@ -3262,16 +3270,16 @@
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2" t="s">
@@ -3293,7 +3301,7 @@
         <v>3</v>
       </c>
       <c r="L24" s="2">
-        <v>6639</v>
+        <v>5217</v>
       </c>
       <c r="M24" s="6" t="s">
         <v>14</v>
@@ -3329,16 +3337,16 @@
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2" t="s">
@@ -3360,7 +3368,7 @@
         <v>3</v>
       </c>
       <c r="L25" s="2">
-        <v>5217</v>
+        <v>7048</v>
       </c>
       <c r="M25" s="6" t="s">
         <v>14</v>
@@ -3396,20 +3404,20 @@
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E26" s="2"/>
+        <v>58</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E26" s="3"/>
       <c r="F26" s="2" t="s">
-        <v>169</v>
+        <v>197</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>162</v>
@@ -3421,13 +3429,13 @@
         <v>158</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>12</v>
+        <v>160</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>3</v>
       </c>
       <c r="L26" s="2">
-        <v>7048</v>
+        <v>6996</v>
       </c>
       <c r="M26" s="6" t="s">
         <v>14</v>
@@ -3436,9 +3444,11 @@
         <v>5</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="P26" s="1"/>
+        <v>54</v>
+      </c>
+      <c r="P26" s="1" t="s">
+        <v>199</v>
+      </c>
       <c r="Q26" s="2" t="s">
         <v>6</v>
       </c>
@@ -3449,7 +3459,7 @@
       <c r="T26" s="2"/>
       <c r="U26" s="2"/>
       <c r="V26" s="2" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="W26" s="2" t="s">
         <v>11</v>
@@ -3463,20 +3473,20 @@
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A27" s="8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>234</v>
+        <v>201</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E27" s="3"/>
+        <v>62</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E27" s="2"/>
       <c r="F27" s="2" t="s">
-        <v>197</v>
+        <v>168</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>162</v>
@@ -3488,13 +3498,13 @@
         <v>158</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>160</v>
+        <v>12</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>3</v>
       </c>
       <c r="L27" s="2">
-        <v>6996</v>
+        <v>3944</v>
       </c>
       <c r="M27" s="6" t="s">
         <v>14</v>
@@ -3505,9 +3515,7 @@
       <c r="O27" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="P27" s="1" t="s">
-        <v>199</v>
-      </c>
+      <c r="P27" s="1"/>
       <c r="Q27" s="2" t="s">
         <v>6</v>
       </c>
@@ -3518,7 +3526,7 @@
       <c r="T27" s="2"/>
       <c r="U27" s="2"/>
       <c r="V27" s="2" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="W27" s="2" t="s">
         <v>11</v>
@@ -3532,16 +3540,16 @@
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A28" s="8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2" t="s">
@@ -3563,7 +3571,7 @@
         <v>3</v>
       </c>
       <c r="L28" s="2">
-        <v>3944</v>
+        <v>7133</v>
       </c>
       <c r="M28" s="6" t="s">
         <v>14</v>
@@ -3599,16 +3607,16 @@
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A29" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2" t="s">
@@ -3630,7 +3638,7 @@
         <v>3</v>
       </c>
       <c r="L29" s="2">
-        <v>7133</v>
+        <v>4285</v>
       </c>
       <c r="M29" s="6" t="s">
         <v>14</v>
@@ -3666,16 +3674,16 @@
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2" t="s">
@@ -3697,7 +3705,7 @@
         <v>3</v>
       </c>
       <c r="L30" s="2">
-        <v>4285</v>
+        <v>4880</v>
       </c>
       <c r="M30" s="6" t="s">
         <v>14</v>
@@ -3733,16 +3741,16 @@
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2" t="s">
@@ -3764,7 +3772,7 @@
         <v>3</v>
       </c>
       <c r="L31" s="2">
-        <v>4880</v>
+        <v>2880</v>
       </c>
       <c r="M31" s="6" t="s">
         <v>14</v>
@@ -3786,10 +3794,10 @@
       <c r="T31" s="2"/>
       <c r="U31" s="2"/>
       <c r="V31" s="2" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="W31" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="X31">
         <v>1</v>
@@ -3800,20 +3808,20 @@
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
-        <v>67</v>
+        <v>215</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>67</v>
+        <v>215</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>152</v>
+        <v>215</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2" t="s">
-        <v>168</v>
+        <v>106</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>162</v>
@@ -3831,18 +3839,20 @@
         <v>3</v>
       </c>
       <c r="L32" s="2">
-        <v>2880</v>
+        <v>6070</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="N32" s="2" t="s">
         <v>5</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="P32" s="1"/>
+        <v>19</v>
+      </c>
+      <c r="P32" s="13">
+        <v>16</v>
+      </c>
       <c r="Q32" s="2" t="s">
         <v>6</v>
       </c>
@@ -3856,7 +3866,7 @@
         <v>10</v>
       </c>
       <c r="W32" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X32">
         <v>1</v>
@@ -3867,16 +3877,16 @@
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A33" s="8" t="s">
-        <v>215</v>
+        <v>31</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>215</v>
+        <v>31</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>215</v>
+        <v>153</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2" t="s">
@@ -3892,13 +3902,13 @@
         <v>158</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>12</v>
+        <v>160</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>3</v>
       </c>
       <c r="L33" s="2">
-        <v>6070</v>
+        <v>5023</v>
       </c>
       <c r="M33" s="6" t="s">
         <v>18</v>
@@ -3909,9 +3919,7 @@
       <c r="O33" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P33" s="13">
-        <v>16</v>
-      </c>
+      <c r="P33" s="1"/>
       <c r="Q33" s="2" t="s">
         <v>6</v>
       </c>
@@ -3936,16 +3944,16 @@
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A34" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2" t="s">
@@ -3967,7 +3975,7 @@
         <v>3</v>
       </c>
       <c r="L34" s="2">
-        <v>5023</v>
+        <v>6189</v>
       </c>
       <c r="M34" s="6" t="s">
         <v>18</v>
@@ -3989,7 +3997,7 @@
       <c r="T34" s="2"/>
       <c r="U34" s="2"/>
       <c r="V34" s="2" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="W34" s="2" t="s">
         <v>11</v>
@@ -4003,20 +4011,20 @@
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A35" s="8" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>229</v>
+        <v>207</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="E35" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E35" s="3"/>
       <c r="F35" s="2" t="s">
-        <v>106</v>
+        <v>169</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>162</v>
@@ -4024,26 +4032,26 @@
       <c r="H35" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="I35" s="2" t="s">
-        <v>158</v>
+      <c r="I35" s="16" t="s">
+        <v>220</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>160</v>
+        <v>12</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>3</v>
       </c>
       <c r="L35" s="2">
-        <v>6189</v>
+        <v>1786</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="N35" s="2" t="s">
         <v>5</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="P35" s="1"/>
       <c r="Q35" s="2" t="s">
@@ -4070,18 +4078,18 @@
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E36" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E36" s="2"/>
       <c r="F36" s="2" t="s">
         <v>169</v>
       </c>
@@ -4101,7 +4109,7 @@
         <v>3</v>
       </c>
       <c r="L36" s="2">
-        <v>1786</v>
+        <v>4060</v>
       </c>
       <c r="M36" s="6" t="s">
         <v>14</v>
@@ -4137,16 +4145,16 @@
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A37" s="8" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>42</v>
+        <v>139</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2" t="s">
@@ -4168,7 +4176,7 @@
         <v>3</v>
       </c>
       <c r="L37" s="2">
-        <v>4060</v>
+        <v>933</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>14</v>
@@ -4204,16 +4212,16 @@
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A38" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="2" t="s">
@@ -4235,7 +4243,7 @@
         <v>3</v>
       </c>
       <c r="L38" s="2">
-        <v>933</v>
+        <v>4936</v>
       </c>
       <c r="M38" s="6" t="s">
         <v>14</v>
@@ -4271,16 +4279,16 @@
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A39" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="2" t="s">
@@ -4302,7 +4310,7 @@
         <v>3</v>
       </c>
       <c r="L39" s="2">
-        <v>4936</v>
+        <v>5356</v>
       </c>
       <c r="M39" s="6" t="s">
         <v>14</v>
@@ -4338,16 +4346,16 @@
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A40" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2" t="s">
@@ -4369,7 +4377,7 @@
         <v>3</v>
       </c>
       <c r="L40" s="2">
-        <v>5356</v>
+        <v>6387</v>
       </c>
       <c r="M40" s="6" t="s">
         <v>14</v>
@@ -4378,7 +4386,7 @@
         <v>5</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>38</v>
+        <v>188</v>
       </c>
       <c r="P40" s="1"/>
       <c r="Q40" s="2" t="s">
@@ -4405,16 +4413,16 @@
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A41" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" s="2" t="s">
@@ -4436,7 +4444,7 @@
         <v>3</v>
       </c>
       <c r="L41" s="2">
-        <v>6387</v>
+        <v>6758</v>
       </c>
       <c r="M41" s="6" t="s">
         <v>14</v>
@@ -4472,16 +4480,16 @@
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A42" s="8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="2" t="s">
@@ -4503,7 +4511,7 @@
         <v>3</v>
       </c>
       <c r="L42" s="2">
-        <v>6758</v>
+        <v>4871</v>
       </c>
       <c r="M42" s="6" t="s">
         <v>14</v>
@@ -4528,91 +4536,24 @@
         <v>34</v>
       </c>
       <c r="W42" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="X42">
         <v>1</v>
       </c>
       <c r="Y42" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A43" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B43" s="15" t="s">
-        <v>227</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="I43" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="J43" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="K43" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L43" s="2">
-        <v>4871</v>
-      </c>
-      <c r="M43" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="N43" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="O43" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="P43" s="1"/>
-      <c r="Q43" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="R43" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="S43" s="2"/>
-      <c r="T43" s="2"/>
-      <c r="U43" s="2"/>
-      <c r="V43" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="W43" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="X43">
-        <v>1</v>
-      </c>
-      <c r="Y43" s="2" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y43">
-    <sortCondition ref="G2:G43"/>
-    <sortCondition ref="I2:I43"/>
-    <sortCondition ref="M2:M43"/>
-    <sortCondition ref="O2:O43"/>
-    <sortCondition ref="P2:P43"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y42">
+    <sortCondition ref="G2:G42"/>
+    <sortCondition ref="I2:I42"/>
+    <sortCondition ref="M2:M42"/>
+    <sortCondition ref="O2:O42"/>
+    <sortCondition ref="P2:P42"/>
   </sortState>
-  <conditionalFormatting sqref="X44:X1048576">
+  <conditionalFormatting sqref="X43:X1048576">
     <cfRule type="colorScale" priority="83">
       <colorScale>
         <cfvo type="min"/>
@@ -4648,7 +4589,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X2:X43">
+  <conditionalFormatting sqref="X2:X42">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -4660,8 +4601,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I43">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="excluded">
+  <conditionalFormatting sqref="I2:I42">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="excluded">
       <formula>NOT(ISERROR(SEARCH("excluded",I2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4672,7 +4613,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E84FD6B7-DAC0-EF4A-B6E8-A6FD2C634E5A}">
-  <dimension ref="A1:AA12"/>
+  <dimension ref="A1:AA13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.1640625" customWidth="1"/>
@@ -5598,8 +5539,113 @@
         <v>3</v>
       </c>
     </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A13" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L13" s="2">
+        <v>5667</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="P13" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="S13" s="2"/>
+      <c r="T13" s="2"/>
+      <c r="U13" s="2"/>
+      <c r="V13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="W13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="X13">
+        <v>5</v>
+      </c>
+      <c r="Y13" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="AA2">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA3">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA1">
+    <cfRule type="colorScale" priority="42">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA4:AA5">
     <cfRule type="colorScale" priority="21">
       <colorScale>
         <cfvo type="min"/>
@@ -5611,8 +5657,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA3">
-    <cfRule type="colorScale" priority="20">
+  <conditionalFormatting sqref="AA7">
+    <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5623,8 +5669,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA1">
-    <cfRule type="colorScale" priority="40">
+  <conditionalFormatting sqref="AA6">
+    <cfRule type="colorScale" priority="44">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5635,8 +5681,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA4:AA5">
-    <cfRule type="colorScale" priority="19">
+  <conditionalFormatting sqref="AA8">
+    <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5647,7 +5693,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA7">
+  <conditionalFormatting sqref="AA9">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -5659,19 +5705,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA6">
-    <cfRule type="colorScale" priority="42">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA8">
+  <conditionalFormatting sqref="AA10">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -5683,7 +5717,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA9">
+  <conditionalFormatting sqref="AA11:AA12">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -5695,28 +5729,21 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA10">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA11:AA12">
+  <conditionalFormatting sqref="X13">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
         <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
       </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I13">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="excluded">
+      <formula>NOT(ISERROR(SEARCH("excluded",I13)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tabular/sublineage/herv_sublineage_data.xlsx
+++ b/tabular/sublineage/herv_sublineage_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/sublineage/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AB9AEB2-E091-B643-A247-E2565DC09B1E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0431F8A2-30C2-CD41-9EB3-F382C4BD78C2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2220" yWindow="860" windowWidth="23060" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/tabular/sublineage/herv_sublineage_data.xlsx
+++ b/tabular/sublineage/herv_sublineage_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/sublineage/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0431F8A2-30C2-CD41-9EB3-F382C4BD78C2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8EBD178-99CE-884D-9138-BEAF327C1F39}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2220" yWindow="860" windowWidth="23060" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -726,9 +726,6 @@
     <t>ERVR-3.Lambda.16A3</t>
   </si>
   <si>
-    <t>ERVR-1.Eta.E</t>
-  </si>
-  <si>
     <t>ERV-1.Eta.E.HQ</t>
   </si>
   <si>
@@ -739,6 +736,9 @@
   </si>
   <si>
     <t>ERV-3.Lambda</t>
+  </si>
+  <si>
+    <t>ERV-1.Eta.E</t>
   </si>
 </sst>
 </file>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>161</v>
@@ -2657,7 +2657,7 @@
         <v>83</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>83</v>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>198</v>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>198</v>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>198</v>
@@ -3407,7 +3407,7 @@
         <v>58</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>58</v>
@@ -5554,7 +5554,7 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>198</v>

--- a/tabular/sublineage/herv_sublineage_data.xlsx
+++ b/tabular/sublineage/herv_sublineage_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/sublineage/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A68AFC1A-C941-9D4A-8C65-3EA898E8005C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B57713E-5B20-B543-8AA7-E4F6153DEE77}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2220" yWindow="860" windowWidth="23060" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1357,17 +1357,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1775,36 +1765,38 @@
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>117</v>
+        <v>57</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>231</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>157</v>
       </c>
       <c r="H2" s="2">
-        <v>9084</v>
+        <v>6996</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>14</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="K2" s="1"/>
+        <v>53</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>197</v>
+      </c>
       <c r="L2" s="2" t="s">
         <v>6</v>
       </c>
@@ -1826,37 +1818,37 @@
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>120</v>
+        <v>213</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>228</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>62</v>
+        <v>213</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>146</v>
+        <v>213</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>169</v>
+        <v>105</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>157</v>
       </c>
       <c r="H3" s="2">
-        <v>4981</v>
+        <v>6070</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>198</v>
+        <v>19</v>
+      </c>
+      <c r="K3" s="13">
+        <v>16</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>6</v>
@@ -1879,34 +1871,34 @@
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>167</v>
+        <v>105</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>157</v>
       </c>
       <c r="H4" s="2">
-        <v>5586</v>
+        <v>5530</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="K4" s="1"/>
       <c r="L4" s="2" t="s">
@@ -1930,19 +1922,19 @@
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>94</v>
+        <v>34</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>90</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>234</v>
@@ -1951,13 +1943,13 @@
         <v>157</v>
       </c>
       <c r="H5" s="2">
-        <v>6918</v>
+        <v>9084</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>14</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>53</v>
+        <v>201</v>
       </c>
       <c r="K5" s="1"/>
       <c r="L5" s="2" t="s">
@@ -1981,19 +1973,19 @@
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>96</v>
+        <v>146</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>105</v>
+        <v>169</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>234</v>
@@ -2002,16 +1994,16 @@
         <v>157</v>
       </c>
       <c r="H6" s="2">
-        <v>4996</v>
+        <v>4981</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K6" s="14">
-        <v>16</v>
+        <v>53</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>198</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>6</v>
@@ -2034,19 +2026,19 @@
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>105</v>
+        <v>167</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>234</v>
@@ -2055,13 +2047,13 @@
         <v>157</v>
       </c>
       <c r="H7" s="2">
-        <v>3556</v>
+        <v>5586</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="2" t="s">
@@ -2085,19 +2077,19 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>105</v>
+        <v>167</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>234</v>
@@ -2106,13 +2098,13 @@
         <v>157</v>
       </c>
       <c r="H8" s="2">
-        <v>5343</v>
+        <v>6918</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="2" t="s">
@@ -2136,28 +2128,28 @@
     </row>
     <row r="9" spans="1:19" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>105</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>157</v>
       </c>
       <c r="H9" s="2">
-        <v>5530</v>
+        <v>4996</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>18</v>
@@ -2165,7 +2157,9 @@
       <c r="J9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K9" s="1"/>
+      <c r="K9" s="14">
+        <v>16</v>
+      </c>
       <c r="L9" s="2" t="s">
         <v>6</v>
       </c>
@@ -2187,16 +2181,16 @@
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>105</v>
@@ -2208,7 +2202,7 @@
         <v>157</v>
       </c>
       <c r="H10" s="2">
-        <v>3329</v>
+        <v>3556</v>
       </c>
       <c r="I10" s="6" t="s">
         <v>18</v>
@@ -2238,16 +2232,16 @@
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>105</v>
@@ -2259,7 +2253,7 @@
         <v>157</v>
       </c>
       <c r="H11" s="2">
-        <v>5685</v>
+        <v>5343</v>
       </c>
       <c r="I11" s="6" t="s">
         <v>18</v>
@@ -2281,7 +2275,7 @@
         <v>11</v>
       </c>
       <c r="R11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S11" s="2" t="b">
         <v>1</v>
@@ -2289,44 +2283,50 @@
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>214</v>
+        <v>111</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>188</v>
+        <v>100</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>230</v>
+        <v>105</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="G12" s="16" t="s">
-        <v>218</v>
+        <v>234</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="H12" s="2">
+        <v>3329</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="K12" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="K12" s="1"/>
       <c r="L12" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>3</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
       <c r="Q12" s="2" t="s">
         <v>11</v>
       </c>
       <c r="R12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S12" s="2" t="b">
         <v>1</v>
@@ -2334,34 +2334,34 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>89</v>
+        <v>29</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>170</v>
+        <v>105</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="G13" s="16" t="s">
-        <v>218</v>
+      <c r="G13" s="2" t="s">
+        <v>157</v>
       </c>
       <c r="H13" s="2">
-        <v>4936</v>
+        <v>5685</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>201</v>
+        <v>19</v>
       </c>
       <c r="K13" s="1"/>
       <c r="L13" s="2" t="s">
@@ -2377,7 +2377,7 @@
         <v>11</v>
       </c>
       <c r="R13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S13" s="2" t="b">
         <v>1</v>
@@ -2385,34 +2385,34 @@
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>112</v>
+        <v>42</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>204</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>101</v>
+        <v>42</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>105</v>
+        <v>168</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="G14" s="16" t="s">
-        <v>218</v>
+      <c r="G14" s="2" t="s">
+        <v>157</v>
       </c>
       <c r="H14" s="2">
-        <v>3037</v>
+        <v>4798</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="2" t="s">
@@ -2436,38 +2436,36 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>229</v>
+        <v>43</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>219</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>82</v>
+        <v>137</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>233</v>
+        <v>168</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>104</v>
+        <v>161</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>157</v>
       </c>
       <c r="H15" s="2">
-        <v>6896</v>
+        <v>6639</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>14</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>17</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="K15" s="1"/>
       <c r="L15" s="2" t="s">
         <v>6</v>
       </c>
@@ -2481,7 +2479,7 @@
         <v>11</v>
       </c>
       <c r="R15">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="S15" s="2" t="b">
         <v>1</v>
@@ -2489,38 +2487,36 @@
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>193</v>
+        <v>49</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>220</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>58</v>
+        <v>143</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>104</v>
+        <v>161</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>157</v>
       </c>
       <c r="H16" s="2">
-        <v>11027</v>
+        <v>5217</v>
       </c>
       <c r="I16" s="6" t="s">
         <v>14</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>197</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="K16" s="1"/>
       <c r="L16" s="2" t="s">
         <v>6</v>
       </c>
@@ -2529,14 +2525,12 @@
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
-      <c r="P16" s="2">
-        <v>2825129</v>
-      </c>
+      <c r="P16" s="2"/>
       <c r="Q16" s="2" t="s">
         <v>11</v>
       </c>
       <c r="R16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S16" s="2" t="b">
         <v>1</v>
@@ -2544,38 +2538,36 @@
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>192</v>
+        <v>51</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>221</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>59</v>
+        <v>145</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>104</v>
+        <v>161</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>157</v>
       </c>
       <c r="H17" s="2">
-        <v>8987</v>
+        <v>7048</v>
       </c>
       <c r="I17" s="6" t="s">
         <v>14</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>197</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="K17" s="1"/>
       <c r="L17" s="2" t="s">
         <v>6</v>
       </c>
@@ -2584,14 +2576,12 @@
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
-      <c r="P17">
-        <v>2825129</v>
-      </c>
+      <c r="P17" s="2"/>
       <c r="Q17" s="2" t="s">
         <v>11</v>
       </c>
       <c r="R17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S17" s="2" t="b">
         <v>1</v>
@@ -2599,28 +2589,28 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>194</v>
+        <v>61</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>199</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>191</v>
+        <v>61</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>191</v>
+        <v>147</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>195</v>
+        <v>167</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>104</v>
+        <v>161</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>157</v>
       </c>
       <c r="H18" s="2">
-        <v>8099</v>
+        <v>3944</v>
       </c>
       <c r="I18" s="6" t="s">
         <v>14</v>
@@ -2628,22 +2618,21 @@
       <c r="J18" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="K18" s="1" t="s">
-        <v>197</v>
-      </c>
+      <c r="K18" s="1"/>
       <c r="L18" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
       <c r="Q18" s="2" t="s">
         <v>11</v>
       </c>
       <c r="R18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S18" s="2" t="b">
         <v>1</v>
@@ -2651,38 +2640,36 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>114</v>
+        <v>63</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>200</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>86</v>
+        <v>63</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>148</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>232</v>
+        <v>167</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>104</v>
+        <v>161</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>157</v>
       </c>
       <c r="H19" s="2">
-        <v>5714</v>
+        <v>7133</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>208</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="K19" s="1"/>
       <c r="L19" s="2" t="s">
         <v>6</v>
       </c>
@@ -2704,34 +2691,34 @@
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>115</v>
+        <v>64</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>209</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>84</v>
+        <v>149</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>232</v>
+        <v>167</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>104</v>
+        <v>161</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>157</v>
       </c>
       <c r="H20" s="2">
-        <v>5246</v>
+        <v>4285</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="K20" s="1"/>
       <c r="L20" s="2" t="s">
@@ -2755,34 +2742,34 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>157</v>
       </c>
       <c r="H21" s="2">
-        <v>8120</v>
+        <v>4880</v>
       </c>
       <c r="I21" s="6" t="s">
         <v>14</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="2" t="s">
@@ -2806,19 +2793,19 @@
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>42</v>
+        <v>151</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>161</v>
@@ -2827,13 +2814,13 @@
         <v>157</v>
       </c>
       <c r="H22" s="2">
-        <v>4798</v>
+        <v>2880</v>
       </c>
       <c r="I22" s="6" t="s">
         <v>14</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="K22" s="1"/>
       <c r="L22" s="2" t="s">
@@ -2846,7 +2833,7 @@
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
       <c r="Q22" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>1</v>
@@ -2857,19 +2844,19 @@
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>168</v>
+        <v>105</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>161</v>
@@ -2878,13 +2865,13 @@
         <v>157</v>
       </c>
       <c r="H23" s="2">
-        <v>6639</v>
+        <v>5023</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="K23" s="1"/>
       <c r="L23" s="2" t="s">
@@ -2908,19 +2895,19 @@
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>168</v>
+        <v>105</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>161</v>
@@ -2929,13 +2916,13 @@
         <v>157</v>
       </c>
       <c r="H24" s="2">
-        <v>5217</v>
+        <v>6189</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="K24" s="1"/>
       <c r="L24" s="2" t="s">
@@ -2959,36 +2946,38 @@
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B25" s="15" t="s">
-        <v>221</v>
+        <v>82</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>229</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>145</v>
+        <v>82</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>168</v>
+        <v>233</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>161</v>
+        <v>104</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>157</v>
       </c>
       <c r="H25" s="2">
-        <v>7048</v>
+        <v>6896</v>
       </c>
       <c r="I25" s="6" t="s">
         <v>14</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="K25" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="L25" s="2" t="s">
         <v>6</v>
       </c>
@@ -3002,7 +2991,7 @@
         <v>11</v>
       </c>
       <c r="R25">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S25" s="2" t="b">
         <v>1</v>
@@ -3010,28 +2999,28 @@
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B26" s="15" t="s">
-        <v>231</v>
+        <v>58</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>193</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>95</v>
+        <v>58</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>195</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>235</v>
+        <v>104</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>157</v>
       </c>
       <c r="H26" s="2">
-        <v>6996</v>
+        <v>11027</v>
       </c>
       <c r="I26" s="6" t="s">
         <v>14</v>
@@ -3050,12 +3039,14 @@
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
-      <c r="P26" s="2"/>
+      <c r="P26" s="2">
+        <v>2825129</v>
+      </c>
       <c r="Q26" s="2" t="s">
         <v>11</v>
       </c>
       <c r="R26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S26" s="2" t="b">
         <v>1</v>
@@ -3063,28 +3054,28 @@
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="B27" s="15" t="s">
-        <v>199</v>
+        <v>59</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>192</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>147</v>
+        <v>59</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>167</v>
+        <v>195</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>161</v>
+        <v>104</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>157</v>
       </c>
       <c r="H27" s="2">
-        <v>3944</v>
+        <v>8987</v>
       </c>
       <c r="I27" s="6" t="s">
         <v>14</v>
@@ -3092,7 +3083,9 @@
       <c r="J27" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="K27" s="1"/>
+      <c r="K27" s="1" t="s">
+        <v>197</v>
+      </c>
       <c r="L27" s="2" t="s">
         <v>6</v>
       </c>
@@ -3101,12 +3094,14 @@
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
-      <c r="P27" s="2"/>
+      <c r="P27">
+        <v>2825129</v>
+      </c>
       <c r="Q27" s="2" t="s">
         <v>11</v>
       </c>
       <c r="R27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S27" s="2" t="b">
         <v>1</v>
@@ -3114,28 +3109,28 @@
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B28" s="15" t="s">
-        <v>200</v>
+        <v>191</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>194</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>63</v>
+        <v>191</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>148</v>
+        <v>191</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>167</v>
+        <v>195</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>157</v>
+        <v>104</v>
+      </c>
+      <c r="G28" s="16" t="s">
+        <v>218</v>
       </c>
       <c r="H28" s="2">
-        <v>7133</v>
+        <v>8099</v>
       </c>
       <c r="I28" s="6" t="s">
         <v>14</v>
@@ -3143,21 +3138,22 @@
       <c r="J28" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="K28" s="1"/>
+      <c r="K28" s="1" t="s">
+        <v>197</v>
+      </c>
       <c r="L28" s="2" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
-      <c r="P28" s="2"/>
       <c r="Q28" s="2" t="s">
         <v>11</v>
       </c>
       <c r="R28">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S28" s="2" t="b">
         <v>1</v>
@@ -3165,36 +3161,38 @@
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="B29" s="15" t="s">
-        <v>209</v>
+        <v>21</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>149</v>
+        <v>21</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>86</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>167</v>
+        <v>232</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>157</v>
+        <v>104</v>
+      </c>
+      <c r="G29" s="16" t="s">
+        <v>218</v>
       </c>
       <c r="H29" s="2">
-        <v>4285</v>
+        <v>5714</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="K29" s="1"/>
+        <v>19</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>208</v>
+      </c>
       <c r="L29" s="2" t="s">
         <v>6</v>
       </c>
@@ -3216,34 +3214,34 @@
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B30" s="15" t="s">
-        <v>210</v>
+        <v>36</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>167</v>
+        <v>232</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>157</v>
+        <v>104</v>
+      </c>
+      <c r="G30" s="16" t="s">
+        <v>218</v>
       </c>
       <c r="H30" s="2">
-        <v>4880</v>
+        <v>5246</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="K30" s="1"/>
       <c r="L30" s="2" t="s">
@@ -3267,34 +3265,34 @@
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>151</v>
+        <v>40</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
+      </c>
+      <c r="G31" s="16" t="s">
+        <v>218</v>
       </c>
       <c r="H31" s="2">
-        <v>2880</v>
+        <v>8120</v>
       </c>
       <c r="I31" s="6" t="s">
         <v>14</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="K31" s="1"/>
       <c r="L31" s="2" t="s">
@@ -3307,7 +3305,7 @@
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
       <c r="Q31" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R31">
         <v>1</v>
@@ -3318,38 +3316,36 @@
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="B32" s="15" t="s">
-        <v>228</v>
+        <v>32</v>
+      </c>
+      <c r="B32" s="17" t="s">
+        <v>116</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>213</v>
+        <v>32</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>105</v>
+        <v>170</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>157</v>
+        <v>234</v>
+      </c>
+      <c r="G32" s="16" t="s">
+        <v>218</v>
       </c>
       <c r="H32" s="2">
-        <v>6070</v>
+        <v>4936</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K32" s="13">
-        <v>16</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="K32" s="1"/>
       <c r="L32" s="2" t="s">
         <v>6</v>
       </c>
@@ -3371,28 +3367,28 @@
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B33" s="15" t="s">
-        <v>226</v>
+        <v>28</v>
+      </c>
+      <c r="B33" s="17" t="s">
+        <v>112</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>152</v>
+        <v>101</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>105</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>157</v>
+        <v>234</v>
+      </c>
+      <c r="G33" s="16" t="s">
+        <v>218</v>
       </c>
       <c r="H33" s="2">
-        <v>5023</v>
+        <v>3037</v>
       </c>
       <c r="I33" s="6" t="s">
         <v>18</v>
@@ -3422,34 +3418,34 @@
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A34" s="8" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>153</v>
+        <v>39</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>105</v>
+        <v>168</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="G34" s="2" t="s">
-        <v>157</v>
+      <c r="G34" s="16" t="s">
+        <v>218</v>
       </c>
       <c r="H34" s="2">
-        <v>6189</v>
+        <v>1786</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="K34" s="1"/>
       <c r="L34" s="2" t="s">
@@ -3473,16 +3469,16 @@
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A35" s="8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>92</v>
+        <v>41</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>168</v>
@@ -3494,7 +3490,7 @@
         <v>218</v>
       </c>
       <c r="H35" s="2">
-        <v>1786</v>
+        <v>4060</v>
       </c>
       <c r="I35" s="6" t="s">
         <v>14</v>
@@ -3524,16 +3520,16 @@
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>41</v>
+        <v>138</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>168</v>
@@ -3545,7 +3541,7 @@
         <v>218</v>
       </c>
       <c r="H36" s="2">
-        <v>4060</v>
+        <v>933</v>
       </c>
       <c r="I36" s="6" t="s">
         <v>14</v>
@@ -3575,16 +3571,16 @@
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A37" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>168</v>
@@ -3596,7 +3592,7 @@
         <v>218</v>
       </c>
       <c r="H37" s="2">
-        <v>933</v>
+        <v>4936</v>
       </c>
       <c r="I37" s="6" t="s">
         <v>14</v>
@@ -3626,16 +3622,16 @@
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>168</v>
@@ -3647,7 +3643,7 @@
         <v>218</v>
       </c>
       <c r="H38" s="2">
-        <v>4936</v>
+        <v>5356</v>
       </c>
       <c r="I38" s="6" t="s">
         <v>14</v>
@@ -3677,16 +3673,16 @@
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A39" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>168</v>
@@ -3698,13 +3694,13 @@
         <v>218</v>
       </c>
       <c r="H39" s="2">
-        <v>5356</v>
+        <v>6387</v>
       </c>
       <c r="I39" s="6" t="s">
         <v>14</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>37</v>
+        <v>187</v>
       </c>
       <c r="K39" s="1"/>
       <c r="L39" s="2" t="s">
@@ -3728,16 +3724,16 @@
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A40" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>168</v>
@@ -3749,7 +3745,7 @@
         <v>218</v>
       </c>
       <c r="H40" s="2">
-        <v>6387</v>
+        <v>6758</v>
       </c>
       <c r="I40" s="6" t="s">
         <v>14</v>
@@ -3779,16 +3775,16 @@
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A41" s="8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>168</v>
@@ -3800,7 +3796,7 @@
         <v>218</v>
       </c>
       <c r="H41" s="2">
-        <v>6758</v>
+        <v>4871</v>
       </c>
       <c r="I41" s="6" t="s">
         <v>14</v>
@@ -3819,7 +3815,7 @@
       <c r="O41" s="2"/>
       <c r="P41" s="2"/>
       <c r="Q41" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R41">
         <v>1</v>
@@ -3830,49 +3826,51 @@
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A42" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="B42" s="15" t="s">
-        <v>225</v>
+        <v>125</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>144</v>
+        <v>125</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>127</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>161</v>
+        <v>104</v>
       </c>
       <c r="G42" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="H42" s="2">
-        <v>4871</v>
-      </c>
+      <c r="H42" s="2"/>
       <c r="I42" s="6" t="s">
         <v>14</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="K42" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="L42" s="2" t="s">
-        <v>6</v>
+        <v>124</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
-      <c r="P42" s="2"/>
+      <c r="P42" s="2">
+        <v>28397686</v>
+      </c>
       <c r="Q42" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="R42">
+      <c r="R42" s="2">
         <v>1</v>
       </c>
       <c r="S42" s="2" t="b">
@@ -3881,19 +3879,19 @@
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A43" s="8" t="s">
-        <v>175</v>
+        <v>128</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>182</v>
+        <v>129</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>179</v>
+        <v>128</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>130</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>104</v>
@@ -3901,30 +3899,26 @@
       <c r="G43" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="H43" s="2">
-        <v>8214</v>
-      </c>
+      <c r="H43" s="2"/>
       <c r="I43" s="6" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>180</v>
+        <v>132</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>6</v>
+        <v>124</v>
       </c>
       <c r="M43" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="N43" s="2">
-        <v>20</v>
-      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" s="2">
-        <v>31167914</v>
+        <v>28397686</v>
       </c>
       <c r="Q43" s="2" t="s">
         <v>10</v>
@@ -3938,19 +3932,19 @@
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="s">
-        <v>176</v>
+        <v>133</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>183</v>
+        <v>134</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>179</v>
+        <v>133</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>135</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>104</v>
@@ -3958,30 +3952,26 @@
       <c r="G44" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="H44" s="2">
-        <v>8214</v>
-      </c>
+      <c r="H44" s="2"/>
       <c r="I44" s="6" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>180</v>
+        <v>136</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>6</v>
+        <v>124</v>
       </c>
       <c r="M44" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="N44" s="2">
-        <v>20</v>
-      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" s="2">
-        <v>31167914</v>
+        <v>28397686</v>
       </c>
       <c r="Q44" s="2" t="s">
         <v>10</v>
@@ -3995,19 +3985,19 @@
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>125</v>
+        <v>38</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>166</v>
+        <v>91</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>165</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>104</v>
@@ -4015,32 +4005,30 @@
       <c r="G45" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="H45" s="2"/>
-      <c r="I45" s="6" t="s">
+      <c r="H45" s="9">
+        <v>7613</v>
+      </c>
+      <c r="I45" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="J45" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="L45" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="M45" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
-      <c r="P45" s="2">
-        <v>28397686</v>
-      </c>
-      <c r="Q45" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="R45" s="2">
-        <v>1</v>
+      <c r="J45" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="K45" s="1"/>
+      <c r="L45" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="M45" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="N45" s="9"/>
+      <c r="O45" s="9"/>
+      <c r="P45" s="9"/>
+      <c r="Q45" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="R45" s="9">
+        <v>3</v>
       </c>
       <c r="S45" s="2" t="b">
         <v>1</v>
@@ -4048,19 +4036,19 @@
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A46" s="8" t="s">
-        <v>128</v>
+        <v>175</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>129</v>
+        <v>182</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>130</v>
+        <v>178</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>179</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>104</v>
@@ -4068,26 +4056,30 @@
       <c r="G46" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="H46" s="2"/>
+      <c r="H46" s="2">
+        <v>8214</v>
+      </c>
       <c r="I46" s="6" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>132</v>
+        <v>180</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>124</v>
+        <v>6</v>
       </c>
       <c r="M46" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="N46" s="2"/>
+      <c r="N46" s="2">
+        <v>20</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" s="2">
-        <v>28397686</v>
+        <v>31167914</v>
       </c>
       <c r="Q46" s="2" t="s">
         <v>10</v>
@@ -4101,19 +4093,19 @@
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A47" s="8" t="s">
-        <v>133</v>
+        <v>176</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>134</v>
+        <v>183</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>135</v>
+        <v>178</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>179</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>104</v>
@@ -4121,26 +4113,30 @@
       <c r="G47" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="H47" s="2"/>
+      <c r="H47" s="2">
+        <v>8214</v>
+      </c>
       <c r="I47" s="6" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>136</v>
+        <v>180</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>124</v>
+        <v>6</v>
       </c>
       <c r="M47" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="N47" s="2"/>
+      <c r="N47" s="2">
+        <v>20</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" s="2">
-        <v>28397686</v>
+        <v>31167914</v>
       </c>
       <c r="Q47" s="2" t="s">
         <v>10</v>
@@ -4154,50 +4150,52 @@
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A48" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="B48" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="E48" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="F48" s="9" t="s">
-        <v>159</v>
+        <v>20</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="G48" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="H48" s="12">
-        <v>2482</v>
-      </c>
-      <c r="I48" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="J48" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="K48" s="9"/>
-      <c r="L48" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="M48" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="N48" s="12"/>
-      <c r="O48" s="12"/>
-      <c r="P48" s="12"/>
-      <c r="Q48" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="R48" s="12">
-        <v>1</v>
+      <c r="H48" s="2">
+        <v>5667</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K48" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
+      <c r="P48" s="2"/>
+      <c r="Q48" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="R48">
+        <v>5</v>
       </c>
       <c r="S48" s="2" t="b">
         <v>1</v>
@@ -4256,19 +4254,19 @@
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>119</v>
+        <v>184</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>159</v>
@@ -4277,15 +4275,17 @@
         <v>218</v>
       </c>
       <c r="H50" s="9">
-        <v>4102</v>
+        <v>9611</v>
       </c>
       <c r="I50" s="10" t="s">
         <v>14</v>
       </c>
       <c r="J50" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="K50" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="L50" s="9" t="s">
         <v>6</v>
       </c>
@@ -4299,7 +4299,7 @@
         <v>11</v>
       </c>
       <c r="R50" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S50" s="2" t="b">
         <v>1</v>
@@ -4307,52 +4307,44 @@
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B51" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="C51" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="E51" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="F51" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="B51" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="F51" s="2" t="s">
         <v>159</v>
       </c>
       <c r="G51" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="H51" s="9">
-        <v>9611</v>
-      </c>
-      <c r="I51" s="10" t="s">
+      <c r="I51" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="J51" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K51" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L51" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="M51" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="N51" s="9"/>
-      <c r="O51" s="9"/>
-      <c r="P51" s="9"/>
-      <c r="Q51" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="R51" s="9">
-        <v>2</v>
+      <c r="J51" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="K51" s="2"/>
+      <c r="L51" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M51" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q51" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="R51">
+        <v>4</v>
       </c>
       <c r="S51" s="2" t="b">
         <v>1</v>
@@ -4360,28 +4352,28 @@
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A52" s="8" t="s">
-        <v>38</v>
+        <v>186</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>118</v>
+        <v>190</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E52" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>104</v>
+        <v>186</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="E52" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>159</v>
       </c>
       <c r="G52" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="H52" s="9">
-        <v>7613</v>
+      <c r="H52" s="12">
+        <v>2482</v>
       </c>
       <c r="I52" s="10" t="s">
         <v>14</v>
@@ -4389,21 +4381,21 @@
       <c r="J52" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K52" s="1"/>
+      <c r="K52" s="9"/>
       <c r="L52" s="9" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="M52" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="N52" s="9"/>
-      <c r="O52" s="9"/>
-      <c r="P52" s="9"/>
+        <v>3</v>
+      </c>
+      <c r="N52" s="12"/>
+      <c r="O52" s="12"/>
+      <c r="P52" s="12"/>
       <c r="Q52" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="R52" s="9">
-        <v>3</v>
+        <v>10</v>
+      </c>
+      <c r="R52" s="12">
+        <v>1</v>
       </c>
       <c r="S52" s="2" t="b">
         <v>1</v>
@@ -4411,64 +4403,62 @@
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A53" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>104</v>
+        <v>52</v>
+      </c>
+      <c r="B53" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>159</v>
       </c>
       <c r="G53" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="H53" s="2">
-        <v>5667</v>
-      </c>
-      <c r="I53" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J53" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K53" s="13" t="s">
-        <v>208</v>
-      </c>
-      <c r="L53" s="2" t="s">
+      <c r="H53" s="9">
+        <v>4102</v>
+      </c>
+      <c r="I53" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="J53" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="K53" s="1"/>
+      <c r="L53" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="M53" s="2" t="s">
+      <c r="M53" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
-      <c r="P53" s="2"/>
-      <c r="Q53" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="R53">
-        <v>5</v>
+      <c r="N53" s="9"/>
+      <c r="O53" s="9"/>
+      <c r="P53" s="9"/>
+      <c r="Q53" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="R53" s="9">
+        <v>3</v>
       </c>
       <c r="S53" s="2" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R42">
-    <sortCondition ref="F2:F42"/>
-    <sortCondition ref="G2:G42"/>
-    <sortCondition ref="I2:I42"/>
-    <sortCondition ref="J2:J42"/>
-    <sortCondition ref="K2:K42"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S53">
+    <sortCondition ref="G2:G53"/>
+    <sortCondition ref="F2:F53"/>
+    <sortCondition ref="I2:I53"/>
+    <sortCondition ref="J2:J53"/>
+    <sortCondition ref="K2:K53"/>
   </sortState>
   <conditionalFormatting sqref="R54:R1048576">
     <cfRule type="colorScale" priority="94">
@@ -4519,7 +4509,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G53">
-    <cfRule type="containsText" dxfId="2" priority="12" operator="containsText" text="excluded">
+    <cfRule type="containsText" dxfId="1" priority="12" operator="containsText" text="excluded">
       <formula>NOT(ISERROR(SEARCH("excluded",G2)))</formula>
     </cfRule>
   </conditionalFormatting>
